--- a/sablonlar/lexbnb-temizlik-sablonu.xlsx
+++ b/sablonlar/lexbnb-temizlik-sablonu.xlsx
@@ -534,7 +534,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ADIM 9 — Araçlar › Excel / CSV yükle ekranına bırakın, türü "Geçmiş temizlik" seçin. Önizlemede hatalı satırları ve nedenini görürsünüz. Yanlış dosya yüklediyseniz aynı ekrandan tek tuşla geri alabilirsiniz.</v>
+        <v>ADIM 9 — Veri ve yardım › Excel / CSV yükle ekranına bırakın, türü "Geçmiş temizlik" seçin. Önizlemede hatalı satırları ve nedenini görürsünüz. Yanlış dosya yüklediyseniz aynı ekrandan tek tuşla geri alabilirsiniz.</v>
       </c>
     </row>
   </sheetData>
@@ -566,7 +566,7 @@
         <v>MULK_KODU_1</v>
       </c>
       <c r="B3" t="str">
-        <v>Yer tutucu — kendi mülk kodunuzu yazın. Kodlarınız hazır yazılı şablon için: uygulamada Araçlar › Excel / CSV yükle › "Kendi mülk kodlarınızla hazır şablon".</v>
+        <v>Yer tutucu — kendi mülk kodunuzu yazın. Kodlarınız hazır yazılı şablon için: uygulamada Veri ve yardım › Excel / CSV yükle › "Kendi mülk kodlarınızla hazır şablon".</v>
       </c>
     </row>
     <row r="4">
@@ -574,7 +574,7 @@
         <v>MULK_KODU_2</v>
       </c>
       <c r="B4" t="str">
-        <v>Yer tutucu — kendi mülk kodunuzu yazın. Kodlarınız hazır yazılı şablon için: uygulamada Araçlar › Excel / CSV yükle › "Kendi mülk kodlarınızla hazır şablon".</v>
+        <v>Yer tutucu — kendi mülk kodunuzu yazın. Kodlarınız hazır yazılı şablon için: uygulamada Veri ve yardım › Excel / CSV yükle › "Kendi mülk kodlarınızla hazır şablon".</v>
       </c>
     </row>
     <row r="6">
